--- a/Example AI Registry.xlsx
+++ b/Example AI Registry.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gsTools\resilient-ai-gov\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gsTools\zoeified\resilient-ai-gov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B7EF363-2F67-4675-9BBD-577AF0588F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4B8FFF-DDF3-40E5-BD36-983625D84381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to Use" sheetId="1" r:id="rId1"/>
@@ -812,31 +812,6 @@
   </cellStyleXfs>
   <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -924,6 +899,31 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1233,6 +1233,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
               <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000001-813E-4D81-884F-0D6C3020A635}"/>
                 </c:ext>
@@ -1260,6 +1261,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
               <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-813E-4D81-884F-0D6C3020A635}"/>
                 </c:ext>
@@ -1287,6 +1289,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
               <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000005-813E-4D81-884F-0D6C3020A635}"/>
                 </c:ext>
@@ -1314,6 +1317,7 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="1"/>
               <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-813E-4D81-884F-0D6C3020A635}"/>
                 </c:ext>
@@ -1793,136 +1797,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="4" spans="2:3" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1945,885 +1949,885 @@
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="15" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="17">
         <v>1</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="17">
         <v>2</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="17">
         <v>2</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="17">
         <v>1</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="18">
         <f t="shared" ref="H6:H35" si="0">IF(COUNT(D6:G6)=4,SUM(D6:G6),"")</f>
         <v>6</v>
       </c>
-      <c r="I6" s="27" t="str">
+      <c r="I6" s="18" t="str">
         <f t="shared" ref="I6:I35" si="1">IF(COUNT(D6:G6)&lt;4,"",CHOOSE(MAX(IF(H6&lt;=6,1,IF(H6&lt;=10,2,IF(H6&lt;=13,3,4))),IF(AND(F6&gt;=3,E6&gt;=3),3,1),IF(AND(D6=4,G6&gt;=3),4,1)),"Clear","Complicated","Complex","Chaotic"))</f>
         <v>Clear</v>
       </c>
-      <c r="J6" s="28" t="str">
+      <c r="J6" s="19" t="str">
         <f t="shared" ref="J6:J35" si="2">IF(I6="","",IF(I6="Clear","Foundation covers it. Confirm classification, vendor review, charter; add a reassessment trigger.",IF(I6="Complicated","Add expert controls: documentation, validation/bias testing, drift monitoring, named owner, human review gate.",IF(I6="Complex","Run a safe-to-fail probe: pilot teams, lightweight guideline, instrument behavior, short feedback loop.","Pre-decide authority: kill switch, named decision-maker, AI-specific IR playbook, preserve inputs and outputs."))))</f>
         <v>Foundation covers it. Confirm classification, vendor review, charter; add a reassessment trigger.</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="17">
         <v>2</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="17">
         <v>2</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="17">
         <v>3</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="17">
         <v>2</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="18">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I7" s="27" t="str">
+      <c r="I7" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complicated</v>
       </c>
-      <c r="J7" s="28" t="str">
+      <c r="J7" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Add expert controls: documentation, validation/bias testing, drift monitoring, named owner, human review gate.</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="17">
         <v>3</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="17">
         <v>3</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="17">
         <v>3</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="17">
         <v>3</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="18">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I8" s="27" t="str">
+      <c r="I8" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complex</v>
       </c>
-      <c r="J8" s="28" t="str">
+      <c r="J8" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Run a safe-to-fail probe: pilot teams, lightweight guideline, instrument behavior, short feedback loop.</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="17">
         <v>4</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="17">
         <v>4</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="17">
         <v>4</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="17">
         <v>4</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="I9" s="27" t="str">
+      <c r="I9" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Chaotic</v>
       </c>
-      <c r="J9" s="28" t="str">
+      <c r="J9" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Pre-decide authority: kill switch, named decision-maker, AI-specific IR playbook, preserve inputs and outputs.</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="17">
         <v>1</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="17">
         <v>2</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="17">
         <v>3</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="17">
         <v>1</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="18">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I10" s="27" t="str">
+      <c r="I10" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complicated</v>
       </c>
-      <c r="J10" s="28" t="str">
+      <c r="J10" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Add expert controls: documentation, validation/bias testing, drift monitoring, named owner, human review gate.</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="17">
         <v>3</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="17">
         <v>2</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="17">
         <v>3</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="17">
         <v>2</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="I11" s="27" t="str">
+      <c r="I11" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complicated</v>
       </c>
-      <c r="J11" s="28" t="str">
+      <c r="J11" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Add expert controls: documentation, validation/bias testing, drift monitoring, named owner, human review gate.</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="17">
         <v>3</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="17">
         <v>3</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="17">
         <v>3</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="17">
         <v>2</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="18">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="I12" s="27" t="str">
+      <c r="I12" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complex</v>
       </c>
-      <c r="J12" s="28" t="str">
+      <c r="J12" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Run a safe-to-fail probe: pilot teams, lightweight guideline, instrument behavior, short feedback loop.</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="17">
         <v>3</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="17">
         <v>2</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="17">
         <v>3</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="17">
         <v>2</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="I13" s="27" t="str">
+      <c r="I13" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complicated</v>
       </c>
-      <c r="J13" s="28" t="str">
+      <c r="J13" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Add expert controls: documentation, validation/bias testing, drift monitoring, named owner, human review gate.</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="17">
         <v>2</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="17">
         <v>2</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="17">
         <v>3</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="17">
         <v>1</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="18">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="I14" s="27" t="str">
+      <c r="I14" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complicated</v>
       </c>
-      <c r="J14" s="28" t="str">
+      <c r="J14" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Add expert controls: documentation, validation/bias testing, drift monitoring, named owner, human review gate.</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="17">
         <v>2</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="17">
         <v>2</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="17">
         <v>3</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="17">
         <v>2</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="18">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I15" s="27" t="str">
+      <c r="I15" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complicated</v>
       </c>
-      <c r="J15" s="28" t="str">
+      <c r="J15" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Add expert controls: documentation, validation/bias testing, drift monitoring, named owner, human review gate.</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="17">
         <v>1</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="17">
         <v>2</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="17">
         <v>3</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="17">
         <v>1</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="18">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I16" s="27" t="str">
+      <c r="I16" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complicated</v>
       </c>
-      <c r="J16" s="28" t="str">
+      <c r="J16" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Add expert controls: documentation, validation/bias testing, drift monitoring, named owner, human review gate.</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="17">
         <v>2</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="17">
         <v>2</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="17">
         <v>3</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="17">
         <v>1</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="18">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="I17" s="27" t="str">
+      <c r="I17" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Complicated</v>
       </c>
-      <c r="J17" s="28" t="str">
+      <c r="J17" s="19" t="str">
         <f t="shared" si="2"/>
         <v>Add expert controls: documentation, validation/bias testing, drift monitoring, named owner, human review gate.</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="27" t="str">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I18" s="27" t="str">
+      <c r="I18" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J18" s="28" t="str">
+      <c r="J18" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="27" t="str">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I19" s="27" t="str">
+      <c r="I19" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J19" s="28" t="str">
+      <c r="J19" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="27" t="str">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I20" s="27" t="str">
+      <c r="I20" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J20" s="28" t="str">
+      <c r="J20" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="27" t="str">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I21" s="27" t="str">
+      <c r="I21" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J21" s="28" t="str">
+      <c r="J21" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="27" t="str">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I22" s="27" t="str">
+      <c r="I22" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J22" s="28" t="str">
+      <c r="J22" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="27" t="str">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I23" s="27" t="str">
+      <c r="I23" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J23" s="28" t="str">
+      <c r="J23" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="27" t="str">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I24" s="27" t="str">
+      <c r="I24" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J24" s="28" t="str">
+      <c r="J24" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="27" t="str">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I25" s="27" t="str">
+      <c r="I25" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J25" s="28" t="str">
+      <c r="J25" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="27" t="str">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I26" s="27" t="str">
+      <c r="I26" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J26" s="28" t="str">
+      <c r="J26" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="27" t="str">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I27" s="27" t="str">
+      <c r="I27" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J27" s="28" t="str">
+      <c r="J27" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="27" t="str">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I28" s="27" t="str">
+      <c r="I28" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J28" s="28" t="str">
+      <c r="J28" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="27" t="str">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I29" s="27" t="str">
+      <c r="I29" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J29" s="28" t="str">
+      <c r="J29" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="27" t="str">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I30" s="27" t="str">
+      <c r="I30" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J30" s="28" t="str">
+      <c r="J30" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="27" t="str">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I31" s="27" t="str">
+      <c r="I31" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J31" s="28" t="str">
+      <c r="J31" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="27" t="str">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I32" s="27" t="str">
+      <c r="I32" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J32" s="28" t="str">
+      <c r="J32" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="27" t="str">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I33" s="27" t="str">
+      <c r="I33" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J33" s="28" t="str">
+      <c r="J33" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="27" t="str">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I34" s="27" t="str">
+      <c r="I34" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J34" s="28" t="str">
+      <c r="J34" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="27" t="str">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I35" s="27" t="str">
+      <c r="I35" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J35" s="28" t="str">
+      <c r="J35" s="19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -2859,7 +2863,7 @@
       <formula>EXACT(I6,"Chaotic")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" errorTitle="Score 1 to 4" error="Enter a whole number from 1 (ordered) to 4 (unordered)." sqref="D6:G35" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>1</formula1>
       <formula2>4</formula2>
@@ -2886,663 +2890,663 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="16" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="16" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="16" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="16" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="16" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="16" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="16" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="25" t="s">
+      <c r="H16" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="H17" s="16" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
     </row>
     <row r="22" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
     </row>
     <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
     </row>
     <row r="35" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="25"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="25"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
+      <c r="A40" s="16"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="25"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
+      <c r="A41" s="16"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
     </row>
     <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="25"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
+      <c r="A44" s="16"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3600,61 +3604,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="4" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="21">
         <f>COUNTIF('AI Registry'!$I$6:$I$35,B5)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="21">
         <f>COUNTIF('AI Registry'!$I$6:$I$35,B6)</f>
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="21">
         <f>COUNTIF('AI Registry'!$I$6:$I$35,B7)</f>
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="21">
         <f>COUNTIF('AI Registry'!$I$6:$I$35,B8)</f>
         <v>1</v>
       </c>
@@ -3681,269 +3685,269 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="7"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="34"/>
     </row>
     <row r="4" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="37"/>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="26" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="28" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="28" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="28" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="28" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="28" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="30" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="38"/>
     </row>
     <row r="14" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="26" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="28" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="28" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="28" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="28" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="30" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="39"/>
     </row>
     <row r="22" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C22" s="26" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="28" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="28" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="28" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="28" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="30" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="C29" s="35"/>
     </row>
     <row r="30" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="35" t="s">
+      <c r="C30" s="26" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="36" t="s">
+      <c r="B31" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="C31" s="37" t="s">
+      <c r="C31" s="28" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="36" t="s">
+      <c r="B32" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="28" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C33" s="28" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="36" t="s">
+      <c r="B34" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="28" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="30" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="C37" s="1"/>
+      <c r="C37" s="36"/>
     </row>
     <row r="38" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="35" t="s">
+      <c r="C38" s="26" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="35" t="s">
+      <c r="C39" s="26" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="35" t="s">
+      <c r="C40" s="26" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="35" t="s">
+      <c r="C41" s="26" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="35" t="s">
+      <c r="C42" s="26" t="s">
         <v>193</v>
       </c>
     </row>
